--- a/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
@@ -789,13 +789,13 @@
         <v>0.375</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>0.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1309,13 +1309,13 @@
         <v>0.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         <v>0.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         <v>0.375</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         <v>0.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
@@ -2164,13 +2164,13 @@
         <v>0.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
@@ -2339,13 +2339,13 @@
         <v>0.28125</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
@@ -2514,13 +2514,13 @@
         <v>0.375</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
@@ -2689,13 +2689,13 @@
         <v>0.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
@@ -2864,13 +2864,13 @@
         <v>0.375</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
@@ -3034,13 +3034,13 @@
         <v>0.44</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
@@ -3209,13 +3209,13 @@
         <v>0.53</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
@@ -3384,13 +3384,13 @@
         <v>0.44</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
@@ -3554,13 +3554,13 @@
         <v>0.53</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
@@ -3729,13 +3729,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
@@ -4079,13 +4079,13 @@
         <v>0.655</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
@@ -4254,13 +4254,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
@@ -4429,13 +4429,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
@@ -4604,13 +4604,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
@@ -4779,13 +4779,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
@@ -4954,13 +4954,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
@@ -5129,13 +5129,13 @@
         <v>0.9375</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
@@ -5304,13 +5304,13 @@
         <v>0.9375</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
@@ -5479,13 +5479,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
@@ -5654,13 +5654,13 @@
         <v>1.25</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A2: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A2: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=0.69~0.690; N2@DRIVE=0.52~0.520; Y@REF=0.44~0.438; D@BORE=0.06~0.062; D1@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A3: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending; page prints B "3/8-14" and A "1/8-24" (thread typos: 3/8-24 UNF / 1/8-27 NPTF intended) - as-printed in Threads note, corrected values used per MS51508 A3</t>
+          <t>legs diverge from MS51508 A3: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending; page prints B "3/8-14" and A "1/8-24" (thread typos: 3/8-24 UNF / 1/8-27 NPTF intended) - as-printed in Threads note, corrected values used per MS51508 A3 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=0.69~0.690; N2@DRIVE=0.52~0.520; Y@REF=0.44~0.438; D@BORE=0.13~0.125; D1@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="C10" t="n">
         <v>0.28</v>
@@ -2101,7 +2101,7 @@
         <v>0.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="T10" t="n">
         <v>0.23</v>
@@ -2125,7 +2125,7 @@
         <v>0.21647</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="AB10" t="n">
         <v>0.5</v>
@@ -2149,7 +2149,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.5600000000000001</v>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086)</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2418,7 +2418,7 @@
         <v>0.1522</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="I12" t="n">
         <v>0.375</v>
@@ -2457,7 +2457,7 @@
         <v>0.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="V12" t="n">
         <v>0.65645</v>
@@ -2505,7 +2505,7 @@
         <v>0.75</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.354</v>
+        <v>0.314</v>
       </c>
       <c r="AL12" t="n">
         <v>0.375</v>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085)</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2938,7 +2938,7 @@
         <v>0.2163</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="I15" t="n">
         <v>0.44</v>
@@ -2977,7 +2977,7 @@
         <v>0.39</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="V15" t="n">
         <v>0.81557</v>
@@ -3025,7 +3025,7 @@
         <v>0.88</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.453</v>
+        <v>0.333</v>
       </c>
       <c r="AL15" t="n">
         <v>0.44</v>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085)</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.42~1.420; N2@DRIVE=1.48~1.480; Y@REF=1.31~1.312; D@BORE=0.61~0.609; D1@BORE=0.94~0.938 | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>B printed "1 1/16-12" (a -16 tube takes 1 5/16-12; non-FG row prints it) - as-printed in Threads note | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>B printed "1 1/16-12" (a -16 tube takes 1 5/16-12; non-FG row prints it) - as-printed in Threads note | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.54~1.540; N2@DRIVE=1.67~1.670; Y@REF=1.63~1.625; D@BORE=0.84~0.844; D1@BORE=1.25~1.250 | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>TUBE OD printed "1" (a -20 is 1 1/4; non-FG row prints it) - as-printed</t>
+          <t>TUBE OD printed "1" (a -20 is 1 1/4; non-FG row prints it) - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.59~1.590; N2@DRIVE=1.64~1.640; Y@REF=1.63~1.625; D@BORE=1.08~1.078; D1@BORE=0.94~0.938</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2503_SW2.xlsx
@@ -1758,7 +1758,7 @@
         <v>37</v>
       </c>
       <c r="R8" t="n">
-        <v>0.531</v>
+        <v>0.52</v>
       </c>
       <c r="S8" t="n">
         <v>0.89</v>
@@ -1864,7 +1864,12 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X755 Side 2 ID = 0.531 (table had 0.52) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X755 Side 2 ID = 0.531 (table had 0.52) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.52 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.531) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.531 -&gt; Air-Way 0.52</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2050,7 +2055,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="C10" t="n">
         <v>0.28</v>
@@ -2101,7 +2106,7 @@
         <v>0.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T10" t="n">
         <v>0.23</v>
@@ -2125,7 +2130,7 @@
         <v>0.21647</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AB10" t="n">
         <v>0.5</v>
@@ -2149,7 +2154,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.5600000000000001</v>
@@ -2204,12 +2209,12 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19]; N2@DRIVE: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.86) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086)</t>
+          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086) | 2026-10-20 Air-Way first: N2@DRIVE OMi/Brennan 0.86 -&gt; Air-Way 0.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2418,7 +2423,7 @@
         <v>0.1522</v>
       </c>
       <c r="H12" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="I12" t="n">
         <v>0.375</v>
@@ -2457,7 +2462,7 @@
         <v>0.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="V12" t="n">
         <v>0.65645</v>
@@ -2505,7 +2510,7 @@
         <v>0.75</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.314</v>
+        <v>0.354</v>
       </c>
       <c r="AL12" t="n">
         <v>0.375</v>
@@ -2554,12 +2559,12 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19]; M2@DRIVE: Air-Way 0.91 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.87) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085)</t>
+          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085) | 2026-10-20 Air-Way first: M2@DRIVE OMi/Brennan 0.87 -&gt; Air-Way 0.91</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2938,7 +2943,7 @@
         <v>0.2163</v>
       </c>
       <c r="H15" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
         <v>0.44</v>
@@ -2977,7 +2982,7 @@
         <v>0.39</v>
       </c>
       <c r="U15" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>0.81557</v>
@@ -3025,7 +3030,7 @@
         <v>0.88</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.333</v>
+        <v>0.453</v>
       </c>
       <c r="AL15" t="n">
         <v>0.44</v>
@@ -3074,12 +3079,12 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19]; M2@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085)</t>
+          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085) | 2026-10-20 Air-Way first: M2@DRIVE OMi/Brennan 0.99 -&gt; Air-Way 1.11</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
